--- a/AsistenciaReto.xlsx
+++ b/AsistenciaReto.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30023"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{64144350-4921-4766-A435-38264EDA7224}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{98FDFB3B-BFBC-41AF-AD8C-8A715154C71A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="15">
   <si>
     <t>Asistencia</t>
   </si>
@@ -46,6 +46,9 @@
   </si>
   <si>
     <t>Ciro Galán Vertiz</t>
+  </si>
+  <si>
+    <t>3 horas</t>
   </si>
   <si>
     <t>Naya Ruiz Ruano</t>
@@ -79,7 +82,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -107,6 +110,14 @@
       <color rgb="FF242424"/>
       <name val="Aptos Narrow"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -162,7 +173,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -170,6 +181,7 @@
     <xf numFmtId="14" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -573,7 +585,9 @@
       <c r="B3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="5"/>
+      <c r="C3" s="5" t="s">
+        <v>5</v>
+      </c>
       <c r="D3" s="5"/>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
@@ -590,7 +604,7 @@
     </row>
     <row r="4" spans="1:16">
       <c r="A4" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>2</v>
@@ -614,7 +628,7 @@
     </row>
     <row r="5" spans="1:16">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>2</v>
@@ -638,12 +652,14 @@
     </row>
     <row r="6" spans="1:16">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="5"/>
+      <c r="C6" s="5" t="s">
+        <v>5</v>
+      </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -660,61 +676,66 @@
     </row>
     <row r="8" spans="1:16">
       <c r="A8" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:16">
       <c r="A9" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>11</v>
+      <c r="B9" s="5" t="s">
+        <v>12</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:16">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B10" s="5"/>
+      <c r="B10" s="5" t="s">
+        <v>12</v>
+      </c>
       <c r="C10" s="5"/>
     </row>
     <row r="11" spans="1:16">
       <c r="A11" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12" spans="1:16">
       <c r="A12" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:16">
       <c r="A13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" s="5"/>
+        <v>8</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>12</v>
+      </c>
       <c r="C13" s="5"/>
+      <c r="E13" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AsistenciaReto.xlsx
+++ b/AsistenciaReto.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30023"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{98FDFB3B-BFBC-41AF-AD8C-8A715154C71A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Usuarios\DAM127\Documents\GitHub\RETO-DAM1-Equipo3\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A963BE38-AA2D-45D8-B2FC-402302D9C149}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -31,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="15">
   <si>
     <t>Asistencia</t>
   </si>
@@ -82,7 +87,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -200,9 +205,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -240,7 +245,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -346,7 +351,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -488,7 +493,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -497,14 +502,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:P13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="18.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="16" width="11.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -554,7 +559,7 @@
         <v>46164</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -564,7 +569,9 @@
       <c r="C2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="5"/>
+      <c r="D2" s="5" t="s">
+        <v>3</v>
+      </c>
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="5"/>
@@ -578,7 +585,7 @@
       <c r="O2" s="5"/>
       <c r="P2" s="5"/>
     </row>
-    <row r="3" spans="1:16">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>4</v>
       </c>
@@ -588,7 +595,9 @@
       <c r="C3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D3" s="5"/>
+      <c r="D3" s="5" t="s">
+        <v>3</v>
+      </c>
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
       <c r="G3" s="5"/>
@@ -602,7 +611,7 @@
       <c r="O3" s="5"/>
       <c r="P3" s="5"/>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
@@ -612,7 +621,9 @@
       <c r="C4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="5"/>
+      <c r="D4" s="5" t="s">
+        <v>3</v>
+      </c>
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
       <c r="G4" s="5"/>
@@ -626,7 +637,7 @@
       <c r="O4" s="5"/>
       <c r="P4" s="5"/>
     </row>
-    <row r="5" spans="1:16">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>7</v>
       </c>
@@ -636,7 +647,9 @@
       <c r="C5" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="5"/>
+      <c r="D5" s="5" t="s">
+        <v>3</v>
+      </c>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
       <c r="G5" s="5"/>
@@ -650,7 +663,7 @@
       <c r="O5" s="5"/>
       <c r="P5" s="5"/>
     </row>
-    <row r="6" spans="1:16">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>8</v>
       </c>
@@ -660,7 +673,9 @@
       <c r="C6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="5"/>
+      <c r="D6" s="5" t="s">
+        <v>3</v>
+      </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
@@ -674,7 +689,7 @@
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
     </row>
-    <row r="8" spans="1:16">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>9</v>
       </c>
@@ -685,7 +700,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>1</v>
       </c>
@@ -696,7 +711,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:16">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>4</v>
       </c>
@@ -705,7 +720,7 @@
       </c>
       <c r="C10" s="5"/>
     </row>
-    <row r="11" spans="1:16">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>6</v>
       </c>
@@ -716,7 +731,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:16">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>7</v>
       </c>
@@ -727,7 +742,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:16">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>8</v>
       </c>
@@ -739,5 +754,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/AsistenciaReto.xlsx
+++ b/AsistenciaReto.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Usuarios\DAM127\Documents\GitHub\RETO-DAM1-Equipo3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A963BE38-AA2D-45D8-B2FC-402302D9C149}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE8D852B-17CB-4B63-8504-E270B28FC954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="13">
   <si>
     <t>Asistencia</t>
   </si>
@@ -44,18 +44,9 @@
     <t>Manuel González Encinas</t>
   </si>
   <si>
-    <t>4 horas</t>
-  </si>
-  <si>
-    <t>5 horas</t>
-  </si>
-  <si>
     <t>Ciro Galán Vertiz</t>
   </si>
   <si>
-    <t>3 horas</t>
-  </si>
-  <si>
     <t>Naya Ruiz Ruano</t>
   </si>
   <si>
@@ -81,6 +72,9 @@
   </si>
   <si>
     <t>Lenguaje de Marcas</t>
+  </si>
+  <si>
+    <t>Horas Totales</t>
   </si>
 </sst>
 </file>
@@ -125,7 +119,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -147,6 +141,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -178,7 +178,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -187,6 +187,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -501,15 +502,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P13"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="18.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="16" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -558,22 +560,29 @@
       <c r="P1" s="4">
         <v>46164</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q1" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
+      <c r="B2" s="5">
+        <v>4</v>
+      </c>
+      <c r="C2" s="6">
+        <v>5</v>
+      </c>
+      <c r="D2" s="6">
+        <v>5</v>
+      </c>
+      <c r="E2" s="5">
+        <v>6</v>
+      </c>
+      <c r="F2" s="5">
+        <v>3</v>
+      </c>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
@@ -584,22 +593,30 @@
       <c r="N2" s="5"/>
       <c r="O2" s="5"/>
       <c r="P2" s="5"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q2" s="8">
+        <f>SUM(B2:P2)</f>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="B3" s="5">
+        <v>4</v>
+      </c>
+      <c r="C3" s="5">
+        <v>3</v>
+      </c>
+      <c r="D3" s="6">
+        <v>3</v>
+      </c>
+      <c r="E3" s="5">
         <v>5</v>
       </c>
-      <c r="D3" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
+      <c r="F3" s="5">
+        <v>3</v>
+      </c>
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
@@ -610,22 +627,30 @@
       <c r="N3" s="5"/>
       <c r="O3" s="5"/>
       <c r="P3" s="5"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q3" s="8">
+        <f t="shared" ref="Q3:Q6" si="0">SUM(B3:P3)</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5">
+        <v>4</v>
+      </c>
+      <c r="C4" s="6">
+        <v>5</v>
+      </c>
+      <c r="D4" s="6">
+        <v>4</v>
+      </c>
+      <c r="E4" s="5">
         <v>6</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
+      <c r="F4" s="5">
+        <v>3</v>
+      </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
@@ -636,22 +661,30 @@
       <c r="N4" s="5"/>
       <c r="O4" s="5"/>
       <c r="P4" s="5"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q4" s="8">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
+        <v>4</v>
+      </c>
+      <c r="B5" s="5">
+        <v>4</v>
+      </c>
+      <c r="C5" s="6">
+        <v>5</v>
+      </c>
+      <c r="D5" s="6">
+        <v>4</v>
+      </c>
+      <c r="E5" s="5">
+        <v>6</v>
+      </c>
+      <c r="F5" s="5">
+        <v>3</v>
+      </c>
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
@@ -662,22 +695,30 @@
       <c r="N5" s="5"/>
       <c r="O5" s="5"/>
       <c r="P5" s="5"/>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q5" s="8">
+        <f t="shared" si="0"/>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="D6" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
+      <c r="B6" s="5">
+        <v>4</v>
+      </c>
+      <c r="C6" s="5">
+        <v>3</v>
+      </c>
+      <c r="D6" s="6">
+        <v>4</v>
+      </c>
+      <c r="E6" s="5">
+        <v>3</v>
+      </c>
+      <c r="F6" s="5">
+        <v>0</v>
+      </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
@@ -688,66 +729,70 @@
       <c r="N6" s="5"/>
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="Q6" s="8">
+        <f t="shared" si="0"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C10" s="5"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C13" s="5"/>
       <c r="E13" s="7"/>

--- a/AsistenciaReto.xlsx
+++ b/AsistenciaReto.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Usuarios\DAM127\Documents\GitHub\RETO-DAM1-Equipo3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE8D852B-17CB-4B63-8504-E270B28FC954}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D259825-FCCA-4586-A77A-067C1CD3E2EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -615,7 +615,7 @@
         <v>5</v>
       </c>
       <c r="F3" s="5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
@@ -629,7 +629,7 @@
       <c r="P3" s="5"/>
       <c r="Q3" s="8">
         <f t="shared" ref="Q3:Q6" si="0">SUM(B3:P3)</f>
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">

--- a/AsistenciaReto.xlsx
+++ b/AsistenciaReto.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Usuarios\DAM127\Documents\GitHub\RETO-DAM1-Equipo3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D259825-FCCA-4586-A77A-067C1CD3E2EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A963BE38-AA2D-45D8-B2FC-402302D9C149}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="15">
   <si>
     <t>Asistencia</t>
   </si>
@@ -44,9 +44,18 @@
     <t>Manuel González Encinas</t>
   </si>
   <si>
+    <t>4 horas</t>
+  </si>
+  <si>
+    <t>5 horas</t>
+  </si>
+  <si>
     <t>Ciro Galán Vertiz</t>
   </si>
   <si>
+    <t>3 horas</t>
+  </si>
+  <si>
     <t>Naya Ruiz Ruano</t>
   </si>
   <si>
@@ -72,9 +81,6 @@
   </si>
   <si>
     <t>Lenguaje de Marcas</t>
-  </si>
-  <si>
-    <t>Horas Totales</t>
   </si>
 </sst>
 </file>
@@ -119,7 +125,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -141,12 +147,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -178,7 +178,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -187,7 +187,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -502,16 +501,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.5703125" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="18.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="16" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -560,29 +558,22 @@
       <c r="P1" s="4">
         <v>46164</v>
       </c>
-      <c r="Q1" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="5">
-        <v>4</v>
-      </c>
-      <c r="C2" s="6">
-        <v>5</v>
-      </c>
-      <c r="D2" s="6">
-        <v>5</v>
-      </c>
-      <c r="E2" s="5">
-        <v>6</v>
-      </c>
-      <c r="F2" s="5">
+      <c r="B2" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>3</v>
       </c>
+      <c r="D2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
@@ -593,30 +584,22 @@
       <c r="N2" s="5"/>
       <c r="O2" s="5"/>
       <c r="P2" s="5"/>
-      <c r="Q2" s="8">
-        <f>SUM(B2:P2)</f>
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="5">
-        <v>4</v>
-      </c>
-      <c r="C3" s="5">
+      <c r="C3" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="6">
-        <v>3</v>
-      </c>
-      <c r="E3" s="5">
-        <v>5</v>
-      </c>
-      <c r="F3" s="5">
-        <v>0</v>
-      </c>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
@@ -627,30 +610,22 @@
       <c r="N3" s="5"/>
       <c r="O3" s="5"/>
       <c r="P3" s="5"/>
-      <c r="Q3" s="8">
-        <f t="shared" ref="Q3:Q6" si="0">SUM(B3:P3)</f>
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="5">
-        <v>4</v>
-      </c>
-      <c r="C4" s="6">
-        <v>5</v>
-      </c>
-      <c r="D4" s="6">
-        <v>4</v>
-      </c>
-      <c r="E4" s="5">
-        <v>6</v>
-      </c>
-      <c r="F4" s="5">
+      <c r="D4" s="5" t="s">
         <v>3</v>
       </c>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
@@ -661,30 +636,22 @@
       <c r="N4" s="5"/>
       <c r="O4" s="5"/>
       <c r="P4" s="5"/>
-      <c r="Q4" s="8">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="5">
-        <v>4</v>
-      </c>
-      <c r="C5" s="6">
-        <v>5</v>
-      </c>
-      <c r="D5" s="6">
-        <v>4</v>
-      </c>
-      <c r="E5" s="5">
-        <v>6</v>
-      </c>
-      <c r="F5" s="5">
+        <v>7</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>3</v>
       </c>
+      <c r="D5" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
@@ -695,30 +662,22 @@
       <c r="N5" s="5"/>
       <c r="O5" s="5"/>
       <c r="P5" s="5"/>
-      <c r="Q5" s="8">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="5">
-        <v>4</v>
-      </c>
-      <c r="C6" s="5">
+      <c r="D6" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="6">
-        <v>4</v>
-      </c>
-      <c r="E6" s="5">
-        <v>3</v>
-      </c>
-      <c r="F6" s="5">
-        <v>0</v>
-      </c>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
@@ -729,70 +688,66 @@
       <c r="N6" s="5"/>
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
-      <c r="Q6" s="8">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C10" s="5"/>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C13" s="5"/>
       <c r="E13" s="7"/>
